--- a/results/Int All Data 0.5/Rando_9_permute.xlsx
+++ b/results/Int All Data 0.5/Rando_9_permute.xlsx
@@ -440,97 +440,97 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7519498595481899</v>
+        <v>0.771525154665871</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7501590286026312</v>
+        <v>0.7711669884767594</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7501590286026312</v>
+        <v>0.7711669884767594</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7452579922427818</v>
+        <v>0.7711669884767594</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7502512088988464</v>
+        <v>0.770092489909424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.743814772490585</v>
+        <v>0.7817487235491807</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7475596849826336</v>
+        <v>0.7788939490320366</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.74684335260441</v>
+        <v>0.7753228421366689</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7498930427097348</v>
+        <v>0.7801633631875524</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.746669547007729</v>
+        <v>0.7673932256629945</v>
       </c>
     </row>
     <row r="12">
@@ -540,727 +540,727 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7438042174948351</v>
+        <v>0.7753545071239185</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7419317612488108</v>
+        <v>0.7696238480981306</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7414814147634836</v>
+        <v>0.7693578622052342</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7418395809525954</v>
+        <v>0.7664925326923402</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7418395809525954</v>
+        <v>0.7653469638202892</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.748276017360857</v>
+        <v>0.7672194200663136</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7407650823852602</v>
+        <v>0.7688258904194414</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7407545273895103</v>
+        <v>0.7691840566085533</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7407545273895103</v>
+        <v>0.7673932256629945</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.758928822737994</v>
+        <v>0.7697265833900957</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7765817012964349</v>
+        <v>0.7697265833900957</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7850855095389015</v>
+        <v>0.7723153720143435</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7891069629195963</v>
+        <v>0.7725919129029897</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7895467544091737</v>
+        <v>0.7607013583575863</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7899049205982853</v>
+        <v>0.7645384511458504</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7899049205982853</v>
+        <v>0.7647122567425313</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7923199036258521</v>
+        <v>0.7636377581751961</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7923199036258521</v>
+        <v>0.7679251974487872</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7863338137029177</v>
+        <v>0.7514207024279305</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7806137096728796</v>
+        <v>0.7514207024279305</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7809718758619913</v>
+        <v>0.7328171705856192</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7868657854887104</v>
+        <v>0.7372889704516412</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7899865458987508</v>
+        <v>0.7393457872900964</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7902525317916471</v>
+        <v>0.7380053028298648</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.790610697980759</v>
+        <v>0.7406046464498623</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7804187940846989</v>
+        <v>0.7337073085605237</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7804187940846989</v>
+        <v>0.7372889704516412</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7779010757651668</v>
+        <v>0.7372889704516412</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7804082390889491</v>
+        <v>0.7410655479309394</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7804082390889491</v>
+        <v>0.7408917423342585</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7739612476849376</v>
+        <v>0.7580414994286229</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7739612476849376</v>
+        <v>0.7460798745785038</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7751279265484883</v>
+        <v>0.7391114663844496</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.769755433711812</v>
+        <v>0.7391114663844496</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.774851385659842</v>
+        <v>0.7398172437669233</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.774851385659842</v>
+        <v>0.7410050326219735</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.779149379929183</v>
+        <v>0.7429696691642131</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7752095518489538</v>
+        <v>0.7429696691642131</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.776284050416289</v>
+        <v>0.7422533367859897</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7770003827945124</v>
+        <v>0.7416291847039816</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7774507292798396</v>
+        <v>0.7416291847039816</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7778088954689515</v>
+        <v>0.7435938212462213</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7753017321451692</v>
+        <v>0.7435938212462213</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7645673014675666</v>
+        <v>0.7512680068227493</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7692234619260193</v>
+        <v>0.751626173011861</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7668084788984525</v>
+        <v>0.7389482157835184</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7685071295477959</v>
+        <v>0.7360012609701589</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.768496574552046</v>
+        <v>0.7446683198135565</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.77136190406494</v>
+        <v>0.74538465219178</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.768957476033123</v>
+        <v>0.74538465219178</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7665530480013061</v>
+        <v>0.7470833028411235</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7565349497019269</v>
+        <v>0.7513707421147144</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7545703131596873</v>
+        <v>0.758154789716338</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7511624568652506</v>
+        <v>0.7577966235272262</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7478467808670295</v>
+        <v>0.7583180403172691</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7566060200066427</v>
+        <v>0.7583180403172691</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7594713495195367</v>
+        <v>0.7523319503943346</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.758130865059305</v>
+        <v>0.7551050996110132</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7522158454410862</v>
+        <v>0.7463669704628999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.774801425346626</v>
+        <v>0.76869430480576</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7759681042101767</v>
+        <v>0.7414553791073006</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7748936056428415</v>
+        <v>0.7414553791073006</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7775851295590545</v>
+        <v>0.7324407090705412</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7775851295590545</v>
+        <v>0.7332386667492302</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7775851295590545</v>
+        <v>0.7322563484781104</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7761524648026075</v>
+        <v>0.7352849285919354</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.774003467667937</v>
+        <v>0.7321536131861451</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7608040936495516</v>
+        <v>0.7411682832229046</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7629319807927224</v>
+        <v>0.7384767593066915</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7629319807927224</v>
+        <v>0.7410655479309394</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7574067923508649</v>
+        <v>0.7417818803091629</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7574067923508649</v>
+        <v>0.7417818803091629</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7581231247290885</v>
+        <v>0.7398066887711733</v>
       </c>
     </row>
     <row r="85">
@@ -1270,717 +1270,717 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7571408064579686</v>
+        <v>0.7511336065435344</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7590948880044585</v>
+        <v>0.759176513304924</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7548074487308674</v>
+        <v>0.7508676206506382</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7490057194003636</v>
+        <v>0.7508676206506382</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7443601139376608</v>
+        <v>0.7530166177853086</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7293699089737167</v>
+        <v>0.7436437815594373</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7293699089737167</v>
+        <v>0.7609778992462326</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7280294245134851</v>
+        <v>0.754541462837971</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7267811203494688</v>
+        <v>0.755165614919979</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7159756193671506</v>
+        <v>0.755165614919979</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7203446839412072</v>
+        <v>0.7572224317584342</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6772359702996493</v>
+        <v>0.7412287985318704</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6745444463834362</v>
+        <v>0.7396117731829928</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6789135109574929</v>
+        <v>0.7416685900214477</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6722821589610507</v>
+        <v>0.7396012181872429</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6658562775485389</v>
+        <v>0.7280083145219853</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6705018830112418</v>
+        <v>0.7273130921352615</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.674615516688152</v>
+        <v>0.731242365219741</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6260526849094522</v>
+        <v>0.7299940610557247</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5962249705867452</v>
+        <v>0.7306182131377328</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5962249705867452</v>
+        <v>0.7448104604229879</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5921007819140851</v>
+        <v>0.7418635056096284</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5936861422757134</v>
+        <v>0.7374838860398218</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5909235480547846</v>
+        <v>0.7342709453335661</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5862779425920818</v>
+        <v>0.7496404264781216</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6107542740696124</v>
+        <v>0.7505200094572761</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6036831305835928</v>
+        <v>0.7519526742137232</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5959062097150996</v>
+        <v>0.7614993160362754</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5969807082824348</v>
+        <v>0.7651626032278585</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5969807082824348</v>
+        <v>0.7515839530288616</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5969807082824348</v>
+        <v>0.7512257868397498</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6138539244881531</v>
+        <v>0.7415053394205167</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.6138539244881531</v>
+        <v>0.7349872777117895</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6338373461081619</v>
+        <v>0.7475836096396665</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6338373461081619</v>
+        <v>0.7495482461819062</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5963565562004267</v>
+        <v>0.7173266588231321</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.563081580265817</v>
+        <v>0.7173266588231321</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.560503346637319</v>
+        <v>0.7660527412027629</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.551967873407603</v>
+        <v>0.7714963043441547</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5528580113825075</v>
+        <v>0.7757731886219961</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5597236842845965</v>
+        <v>0.7567587156118238</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5577590477423567</v>
+        <v>0.7529926931282755</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.6444479315022996</v>
+        <v>0.7464218564407992</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6444479315022996</v>
+        <v>0.7164463721775942</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.6089528881283037</v>
+        <v>0.7157300397993707</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5852139990204964</v>
+        <v>0.7157300397993707</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5719224447058956</v>
+        <v>0.7079636739266273</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5862068722873661</v>
+        <v>0.7086800063048508</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5689438249052865</v>
+        <v>0.7112793499248484</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5689438249052865</v>
+        <v>0.6940662628559848</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5763520245889181</v>
+        <v>0.6985275077262569</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5911578689604314</v>
+        <v>0.6993254654049459</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5930303252064557</v>
+        <v>0.6993254654049459</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.6072331274874607</v>
+        <v>0.6975346344593871</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4932553577158426</v>
+        <v>0.6975346344593871</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4932553577158426</v>
+        <v>0.7361771775659898</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4744540956198176</v>
+        <v>0.7140285744844941</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4744540956198176</v>
+        <v>0.6925991184467549</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4731241661553358</v>
+        <v>0.6924358678458239</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4817095996982678</v>
+        <v>0.6904712313035842</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4813514335091561</v>
+        <v>0.6904712313035842</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4887174132097883</v>
+        <v>0.6904712313035842</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4936290045653875</v>
+        <v>0.6901130651144725</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5067967135965233</v>
+        <v>0.5436871274086501</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5055983697457231</v>
+        <v>0.5076734819101446</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4944452575700429</v>
+        <v>0.5009816146047366</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4944452575700429</v>
+        <v>0.5024142793611835</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5010660545707354</v>
+        <v>0.5361001964636543</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5010660545707354</v>
+        <v>0.5206913100016325</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5010660545707354</v>
+        <v>0.5206913100016325</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4987432518393839</v>
+        <v>0.522716461852838</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4890910600593332</v>
+        <v>0.5040897090198772</v>
       </c>
     </row>
   </sheetData>
